--- a/Fase 2/Evidencias proyecto/Evidencias de sistema/Base de datos/Diccionario de datos.xlsx
+++ b/Fase 2/Evidencias proyecto/Evidencias de sistema/Base de datos/Diccionario de datos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29518"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C60C56-FE3D-401E-8DA8-31592D33F4E0}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B9AA69-6676-4033-82DE-2359C48E4024}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
-  <si>
-    <t>Usuario</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="100">
+  <si>
+    <t>users</t>
   </si>
   <si>
     <t>Campo</t>
@@ -69,130 +69,175 @@
     <t>PK</t>
   </si>
   <si>
+    <t>fullName</t>
+  </si>
+  <si>
+    <t>Nombre completo del usuario</t>
+  </si>
+  <si>
+    <t>Texto</t>
+  </si>
+  <si>
+    <t>No nulo</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Correo electrónico del usuario</t>
+  </si>
+  <si>
+    <t>No nulo, Formato email válido, único</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>opcional</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>rol del usuario (admin / cliente)</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>fecha de registro</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Default CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>uid</t>
+  </si>
+  <si>
+    <t>UID autenticacion (Firebase/ auth)</t>
+  </si>
+  <si>
+    <t>unico</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>id_producto</t>
+  </si>
+  <si>
+    <t>Identificador único del producto</t>
+  </si>
+  <si>
     <t>nombre</t>
   </si>
   <si>
-    <t>Nombre del usuario</t>
-  </si>
-  <si>
-    <t>Texto</t>
-  </si>
-  <si>
-    <t>No nulo</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Correo electrónico del usuario</t>
-  </si>
-  <si>
-    <t>Formato email válido, único</t>
-  </si>
-  <si>
-    <t>contraseña</t>
-  </si>
-  <si>
-    <t>Contraseña encriptada</t>
-  </si>
-  <si>
-    <t>fecha_registro</t>
-  </si>
-  <si>
-    <t>Fecha de creación de la cuenta</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>AAAA-MM-DD</t>
-  </si>
-  <si>
-    <t>Tienda</t>
-  </si>
-  <si>
-    <t>id_tienda</t>
-  </si>
-  <si>
-    <t>Identificador único de la tienda</t>
-  </si>
-  <si>
-    <t>nombre_tienda</t>
-  </si>
-  <si>
-    <t>Nombre comercial de la tienda</t>
-  </si>
-  <si>
-    <t>url_tienda</t>
-  </si>
-  <si>
-    <t>Página principal de la tienda</t>
-  </si>
-  <si>
-    <t>Formato URL válido</t>
-  </si>
-  <si>
-    <t>contacto</t>
-  </si>
-  <si>
-    <t>Correo o teléfono de contacto</t>
+    <t>Nombre del producto</t>
+  </si>
+  <si>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>Categoria (“Perro”, “Gato”)</t>
+  </si>
+  <si>
+    <t>marca</t>
+  </si>
+  <si>
+    <t>Marca comercial</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>Descripción breve</t>
   </si>
   <si>
     <t>Opcional</t>
   </si>
   <si>
-    <t>Producto</t>
-  </si>
-  <si>
-    <t>id_producto</t>
-  </si>
-  <si>
-    <t>Identificador único del producto</t>
-  </si>
-  <si>
-    <t>nombre_producto</t>
-  </si>
-  <si>
-    <t>Nombre del producto</t>
-  </si>
-  <si>
-    <t>categoria</t>
-  </si>
-  <si>
-    <t>Tipo de producto</t>
-  </si>
-  <si>
-    <t>(“Alimento”, “Accesorio”, “Higiene”)</t>
-  </si>
-  <si>
-    <t>marca</t>
-  </si>
-  <si>
-    <t>Marca comercial</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>Descripción breve</t>
-  </si>
-  <si>
-    <t>Tienda que ofrece el producto</t>
-  </si>
-  <si>
-    <t>Debe existir en Tienda</t>
+    <t>imagen</t>
+  </si>
+  <si>
+    <t>URL de imagen</t>
+  </si>
+  <si>
+    <t>precio_minimo</t>
+  </si>
+  <si>
+    <t>Precio mas bajo encontrado</t>
+  </si>
+  <si>
+    <t>Decimal</t>
+  </si>
+  <si>
+    <t>Mayor a 0</t>
+  </si>
+  <si>
+    <t>tienda_mas_barata</t>
+  </si>
+  <si>
+    <t>Nombre de la tienda con menor precio</t>
+  </si>
+  <si>
+    <t>last_updated</t>
+  </si>
+  <si>
+    <t>Ultima fecha de actualizacion</t>
+  </si>
+  <si>
+    <t>(MAP precios)</t>
+  </si>
+  <si>
+    <t>id_precio</t>
+  </si>
+  <si>
+    <t>identificador unico</t>
+  </si>
+  <si>
+    <t>PK, autoincremental</t>
+  </si>
+  <si>
+    <t>producto asociado</t>
+  </si>
+  <si>
+    <t>FK → Producto (id_producto)</t>
   </si>
   <si>
     <t>FK</t>
   </si>
   <si>
-    <t>Historial_precios</t>
-  </si>
-  <si>
-    <t>id_historial</t>
+    <t>nombre de la tienda</t>
+  </si>
+  <si>
+    <t>precio</t>
+  </si>
+  <si>
+    <t>precio encontrado</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>URL del producto en la tienda</t>
+  </si>
+  <si>
+    <t>Formato URL valido</t>
+  </si>
+  <si>
+    <t>historico_Precios</t>
+  </si>
+  <si>
+    <t>id_historico</t>
   </si>
   <si>
     <t>Identificador del historial de precios</t>
@@ -201,25 +246,16 @@
     <t>Producto al que pertenece el historial</t>
   </si>
   <si>
-    <t>Debe existir en Producto</t>
-  </si>
-  <si>
-    <t>precio</t>
-  </si>
-  <si>
-    <t>Precio registrado</t>
-  </si>
-  <si>
-    <t>Decimal</t>
-  </si>
-  <si>
-    <t>Mayor a 0</t>
+    <t>Precio minimo registrado ese dia</t>
+  </si>
+  <si>
+    <t>fecha</t>
   </si>
   <si>
     <t>Fecha de captura del precio</t>
   </si>
   <si>
-    <t>Favorito</t>
+    <t>favorites</t>
   </si>
   <si>
     <t>id_favorito</t>
@@ -228,25 +264,40 @@
     <t>Identificador del favorito</t>
   </si>
   <si>
-    <t>Autoincremental</t>
-  </si>
-  <si>
     <t>Usuario que marcó favorito</t>
   </si>
   <si>
-    <t>Debe existir en Usuario</t>
+    <t>FK → Usuario (id_usuario)</t>
   </si>
   <si>
     <t>Producto marcado como favorito</t>
   </si>
   <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>nombre del producto guardado</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>imagen almacenada</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>precio en el momento guardado</t>
+  </si>
+  <si>
     <t>fecha_guardado</t>
   </si>
   <si>
     <t>Fecha en que se marcó el favorito</t>
   </si>
   <si>
-    <t>Reseña</t>
+    <t>reseña</t>
   </si>
   <si>
     <t>id_resena</t>
@@ -261,22 +312,22 @@
     <t>Producto reseñado</t>
   </si>
   <si>
-    <t>comentario</t>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>Valoración numérica (1 - 5)</t>
+  </si>
+  <si>
+    <t>text</t>
   </si>
   <si>
     <t>Texto de la reseña</t>
   </si>
   <si>
-    <t>calificacion</t>
-  </si>
-  <si>
-    <t>Valoración numérica</t>
-  </si>
-  <si>
-    <t>1 a 5</t>
-  </si>
-  <si>
-    <t>fecha_resena</t>
+    <t>username</t>
+  </si>
+  <si>
+    <t>nombre del usuario quien publico</t>
   </si>
   <si>
     <t>Fecha de publicación</t>
@@ -286,7 +337,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +351,12 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -309,7 +366,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -345,18 +402,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
+      <alignment horizontal="right" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,13 +791,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G52"/>
+  <dimension ref="B2:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="7"/>
+    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
@@ -716,7 +816,7 @@
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -736,7 +836,7 @@
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="8">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -756,7 +856,7 @@
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="8">
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -774,7 +874,7 @@
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="8">
         <v>150</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -792,188 +892,233 @@
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2">
-        <v>255</v>
+      <c r="E7" s="8">
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="E9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>60</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="2"/>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>11</v>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="2">
-        <v>150</v>
+        <v>3</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="2">
-        <v>255</v>
+        <v>9</v>
+      </c>
+      <c r="E15" s="8">
+        <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="8">
         <v>150</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G16" s="2"/>
     </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8">
+        <v>100</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8">
+        <v>255</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="2" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="E20" s="8">
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2">
-        <v>11</v>
+        <v>48</v>
+      </c>
+      <c r="E21" s="8">
+        <v>10.199999999999999</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G21" s="2"/>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="2">
-        <v>150</v>
+      <c r="E22" s="8">
+        <v>100</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>15</v>
@@ -982,420 +1127,555 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="2">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="2">
-        <v>100</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="2">
-        <v>255</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="2"/>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="2">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>51</v>
+      <c r="E27" s="8">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="8">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="8">
+        <v>100</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="2" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>4</v>
+        <v>48</v>
+      </c>
+      <c r="E30" s="8">
+        <v>10.199999999999999</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="8">
+        <v>255</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="2">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="2" t="s">
+      <c r="E37" s="8">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="2">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="1" t="s">
-        <v>62</v>
+      <c r="G37" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="2" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E38" s="8">
+        <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2">
-        <v>11</v>
+        <v>48</v>
+      </c>
+      <c r="E39" s="8">
+        <v>10.199999999999999</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G39" s="2"/>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="2" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="2">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="2">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="1" t="s">
-        <v>71</v>
+      <c r="E45" s="8">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E46" s="8">
+        <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="8">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="2" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="2">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E48" s="8">
+        <v>150</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="2" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="2">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E49" s="8">
+        <v>255</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="2">
-        <v>255</v>
+        <v>48</v>
+      </c>
+      <c r="E50" s="8">
+        <v>10.199999999999999</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="8">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="8">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="G57" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E58" s="8">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="8">
         <v>1</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="F59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="8">
+        <v>255</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8">
+        <v>150</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" s="2"/>
+      <c r="C62" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
